--- a/artfynd/A 60354-2024 artfynd.xlsx
+++ b/artfynd/A 60354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,215 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122409996</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98185</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Björkesjö, Björkesjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>530957</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6336801</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åseda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122410051</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57527</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björkesjö, Björkesjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>530937</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6336832</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åseda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60354-2024 artfynd.xlsx
+++ b/artfynd/A 60354-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122359203</v>
       </c>
       <c r="B2" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60354-2024 artfynd.xlsx
+++ b/artfynd/A 60354-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122359203</v>
       </c>
       <c r="B2" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122409996</v>
       </c>
       <c r="B3" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>122410051</v>
       </c>
       <c r="B4" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 60354-2024 artfynd.xlsx
+++ b/artfynd/A 60354-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122359203</v>
       </c>
       <c r="B2" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122409996</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60354-2024 artfynd.xlsx
+++ b/artfynd/A 60354-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122359203</v>
       </c>
       <c r="B2" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -780,7 +775,7 @@
         <v>122409996</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,11 +789,6 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -896,11 +886,6 @@
       </c>
       <c r="E4" t="n">
         <v>103021</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 60354-2024 artfynd.xlsx
+++ b/artfynd/A 60354-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122359203</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -775,7 +780,7 @@
         <v>122409996</v>
       </c>
       <c r="B3" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,6 +794,11 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -872,7 +882,7 @@
         <v>122410051</v>
       </c>
       <c r="B4" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -886,6 +896,11 @@
       </c>
       <c r="E4" t="n">
         <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 60354-2024 artfynd.xlsx
+++ b/artfynd/A 60354-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122359203</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122409996</v>
+        <v>122410051</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björkesjö, Björkesjö, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530957</v>
+        <v>530937</v>
       </c>
       <c r="R3" t="n">
-        <v>6336801</v>
+        <v>6336832</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122410051</v>
+        <v>122409996</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,46 +896,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkesjö, Björkesjö, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530937</v>
+        <v>530957</v>
       </c>
       <c r="R4" t="n">
-        <v>6336832</v>
+        <v>6336801</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 60354-2024 artfynd.xlsx
+++ b/artfynd/A 60354-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122410051</v>
+        <v>122409996</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björkesjö, Björkesjö, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530937</v>
+        <v>530957</v>
       </c>
       <c r="R3" t="n">
-        <v>6336832</v>
+        <v>6336801</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122409996</v>
+        <v>122410051</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,41 +891,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkesjö, Björkesjö, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530957</v>
+        <v>530937</v>
       </c>
       <c r="R4" t="n">
-        <v>6336801</v>
+        <v>6336832</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 60354-2024 artfynd.xlsx
+++ b/artfynd/A 60354-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122359203</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122409996</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60354-2024 artfynd.xlsx
+++ b/artfynd/A 60354-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122409996</v>
+        <v>122410051</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björkesjö, Björkesjö, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530957</v>
+        <v>530937</v>
       </c>
       <c r="R3" t="n">
-        <v>6336801</v>
+        <v>6336832</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122410051</v>
+        <v>122409996</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,46 +896,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkesjö, Björkesjö, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530937</v>
+        <v>530957</v>
       </c>
       <c r="R4" t="n">
-        <v>6336832</v>
+        <v>6336801</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 60354-2024 artfynd.xlsx
+++ b/artfynd/A 60354-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122359203</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122410051</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>122409996</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 60354-2024 artfynd.xlsx
+++ b/artfynd/A 60354-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122359203</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>122409996</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 60354-2024 artfynd.xlsx
+++ b/artfynd/A 60354-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122410051</v>
+        <v>122409996</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björkesjö, Björkesjö, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530937</v>
+        <v>530957</v>
       </c>
       <c r="R3" t="n">
-        <v>6336832</v>
+        <v>6336801</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122409996</v>
+        <v>122410051</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,41 +891,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkesjö, Björkesjö, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530957</v>
+        <v>530937</v>
       </c>
       <c r="R4" t="n">
-        <v>6336801</v>
+        <v>6336832</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 60354-2024 artfynd.xlsx
+++ b/artfynd/A 60354-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>122409996</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>122410051</v>
       </c>
       <c r="B4" t="n">
-        <v>57537</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
